--- a/assets/translations/Polish.Poland.pl-PL.xlsx
+++ b/assets/translations/Polish.Poland.pl-PL.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Irena Fryc\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zauner/Documents/Arbeit/12-TUM/Repos_Misc/2024-04_Ladenburg_Roundtable/LCS/assets/translations/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6846EBA0-7940-4ADF-B294-0CC18C1525FA}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57E8D6CE-F88B-124D-A880-7D8B30DB7D1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="30720" windowHeight="13380" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10700" yWindow="4360" windowWidth="29520" windowHeight="18620" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Contributors" sheetId="2" r:id="rId1"/>
     <sheet name="Statements" sheetId="1" r:id="rId2"/>
     <sheet name="Key messages" sheetId="4" r:id="rId3"/>
+    <sheet name="Misc" sheetId="5" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="216">
   <si>
     <t>Number</t>
   </si>
@@ -678,12 +679,45 @@
   <si>
     <t>Naukowcy prowadzą badania dotyczące wpływu światła na procesy fizjologiczne i zdrowie.</t>
   </si>
+  <si>
+    <t>References</t>
+  </si>
+  <si>
+    <t>Consensus statements</t>
+  </si>
+  <si>
+    <t>Consensus statements (Polish)</t>
+  </si>
+  <si>
+    <t>Key messages</t>
+  </si>
+  <si>
+    <t>Kluczowe wiadomości</t>
+  </si>
+  <si>
+    <t>Bibliografia</t>
+  </si>
+  <si>
+    <t>Rozdział</t>
+  </si>
+  <si>
+    <t>Numer</t>
+  </si>
+  <si>
+    <t>Oświadczenie</t>
+  </si>
+  <si>
+    <t>Uproszczone oświadczenie</t>
+  </si>
+  <si>
+    <t>Informacje kontekstowe</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -810,6 +844,28 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="15"/>
+      <color theme="9"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -831,7 +887,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -885,21 +941,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
@@ -1001,11 +1042,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1015,16 +1057,10 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1034,10 +1070,10 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1056,22 +1092,22 @@
     <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -1082,10 +1118,16 @@
     <xf numFmtId="0" fontId="17" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hiperłącze" xfId="1" builtinId="8"/>
-    <cellStyle name="Normalny" xfId="0" builtinId="0"/>
+  <cellStyles count="3">
+    <cellStyle name="Link" xfId="1" builtinId="8"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Standard 2" xfId="2" xr:uid="{72EB64ED-F184-4E43-9701-64153E759F07}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1403,145 +1445,145 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G11"/>
-  <sheetFormatPr defaultColWidth="10.8984375" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="24.3984375" style="2" customWidth="1"/>
+    <col min="1" max="1" width="24.33203125" style="2" customWidth="1"/>
     <col min="2" max="3" width="21.5" style="2" customWidth="1"/>
-    <col min="4" max="4" width="28.09765625" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="42.8984375" style="2" customWidth="1"/>
-    <col min="6" max="6" width="40.09765625" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="10.8984375" style="2"/>
+    <col min="4" max="4" width="28.1640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="42.83203125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="40.1640625" style="2" customWidth="1"/>
+    <col min="7" max="16384" width="10.83203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.6">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="B1" s="16" t="s">
+      <c r="B1" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="C1" s="16" t="s">
+      <c r="C1" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="D1" s="16" t="s">
+      <c r="D1" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="E1" s="16" t="s">
+      <c r="E1" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="F1" s="16" t="s">
+      <c r="F1" s="14" t="s">
         <v>67</v>
       </c>
       <c r="G1" s="1"/>
     </row>
-    <row r="2" spans="1:7" s="11" customFormat="1" ht="15.6">
-      <c r="A2" s="11" t="s">
+    <row r="2" spans="1:7" s="9" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="C2" s="17" t="s">
+      <c r="C2" s="15" t="s">
         <v>171</v>
       </c>
-      <c r="D2" s="30" t="s">
+      <c r="D2" s="28" t="s">
         <v>172</v>
       </c>
-      <c r="E2" s="17" t="s">
+      <c r="E2" s="15" t="s">
         <v>83</v>
       </c>
-      <c r="F2" s="18" t="s">
+      <c r="F2" s="16" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="3" spans="1:7" s="11" customFormat="1">
-      <c r="A3" s="11" t="s">
+    <row r="3" spans="1:7" s="9" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="B3" s="17" t="s">
+      <c r="B3" s="15" t="s">
         <v>85</v>
       </c>
-      <c r="C3" s="17" t="s">
+      <c r="C3" s="15" t="s">
         <v>99</v>
       </c>
-      <c r="D3" s="18" t="s">
+      <c r="D3" s="16" t="s">
         <v>88</v>
       </c>
-      <c r="E3" s="17" t="s">
+      <c r="E3" s="15" t="s">
         <v>83</v>
       </c>
-      <c r="F3" s="18" t="s">
+      <c r="F3" s="16" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="4" spans="1:7" s="11" customFormat="1">
-      <c r="A4" s="11" t="s">
+    <row r="4" spans="1:7" s="9" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="B4" s="17" t="s">
+      <c r="B4" s="15" t="s">
         <v>87</v>
       </c>
-      <c r="C4" s="17" t="s">
+      <c r="C4" s="15" t="s">
         <v>99</v>
       </c>
-      <c r="D4" s="18" t="s">
+      <c r="D4" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="E4" s="17" t="s">
+      <c r="E4" s="15" t="s">
         <v>83</v>
       </c>
-      <c r="F4" s="17" t="s">
+      <c r="F4" s="15" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="5" spans="1:7" s="11" customFormat="1">
-      <c r="B5" s="17"/>
-      <c r="C5" s="17"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="17"/>
-      <c r="F5" s="17"/>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="B6" s="19"/>
-      <c r="C6" s="19"/>
-      <c r="D6" s="19"/>
-      <c r="E6" s="19"/>
-      <c r="F6" s="19"/>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="B7" s="19"/>
-      <c r="C7" s="19"/>
-      <c r="D7" s="19"/>
-      <c r="E7" s="19"/>
-      <c r="F7" s="19"/>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="B8" s="19"/>
-      <c r="C8" s="19"/>
-      <c r="D8" s="19"/>
-      <c r="E8" s="19"/>
-      <c r="F8" s="19"/>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="B9" s="19"/>
-      <c r="C9" s="19"/>
-      <c r="D9" s="19"/>
-      <c r="E9" s="19"/>
-      <c r="F9" s="19"/>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="B10" s="19"/>
-      <c r="C10" s="19"/>
-      <c r="D10" s="19"/>
-      <c r="E10" s="19"/>
-      <c r="F10" s="19"/>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="B11" s="19"/>
-      <c r="C11" s="19"/>
-      <c r="D11" s="19"/>
-      <c r="E11" s="19"/>
-      <c r="F11" s="19"/>
+    <row r="5" spans="1:7" s="9" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B5" s="15"/>
+      <c r="C5" s="15"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="15"/>
+      <c r="F5" s="15"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B6" s="17"/>
+      <c r="C6" s="17"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="17"/>
+      <c r="F6" s="17"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B7" s="17"/>
+      <c r="C7" s="17"/>
+      <c r="D7" s="17"/>
+      <c r="E7" s="17"/>
+      <c r="F7" s="17"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B8" s="17"/>
+      <c r="C8" s="17"/>
+      <c r="D8" s="17"/>
+      <c r="E8" s="17"/>
+      <c r="F8" s="17"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B9" s="17"/>
+      <c r="C9" s="17"/>
+      <c r="D9" s="17"/>
+      <c r="E9" s="17"/>
+      <c r="F9" s="17"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B10" s="17"/>
+      <c r="C10" s="17"/>
+      <c r="D10" s="17"/>
+      <c r="E10" s="17"/>
+      <c r="F10" s="17"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B11" s="17"/>
+      <c r="C11" s="17"/>
+      <c r="D11" s="17"/>
+      <c r="E11" s="17"/>
+      <c r="F11" s="17"/>
     </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
@@ -1558,796 +1600,877 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I27"/>
-  <sheetFormatPr defaultColWidth="11.5" defaultRowHeight="15.6"/>
+  <dimension ref="A1:J27"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="49.59765625" customWidth="1"/>
-    <col min="2" max="2" width="25.09765625" customWidth="1"/>
-    <col min="3" max="3" width="10" customWidth="1"/>
-    <col min="4" max="8" width="42.3984375" customWidth="1"/>
-    <col min="9" max="9" width="42.3984375" style="9" customWidth="1"/>
+    <col min="1" max="1" width="49.6640625" customWidth="1"/>
+    <col min="2" max="2" width="25.1640625" customWidth="1"/>
+    <col min="3" max="4" width="10" customWidth="1"/>
+    <col min="5" max="9" width="42.33203125" customWidth="1"/>
+    <col min="10" max="10" width="42.33203125" style="7" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>69</v>
       </c>
-      <c r="B1" s="13" t="s">
-        <v>62</v>
+      <c r="B1" t="s">
+        <v>211</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" t="s">
+        <v>212</v>
+      </c>
+      <c r="E1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" t="s">
+        <v>213</v>
+      </c>
+      <c r="G1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" t="s">
+        <v>214</v>
+      </c>
+      <c r="I1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="I1" s="6" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" s="10" customFormat="1" ht="90">
+      <c r="J1" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" s="8" customFormat="1" ht="119" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>70</v>
       </c>
-      <c r="B2" s="31" t="s">
+      <c r="B2" s="29" t="s">
         <v>102</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="10">
         <v>1</v>
       </c>
-      <c r="D2" s="20" t="s">
+      <c r="D2" s="10">
+        <v>1</v>
+      </c>
+      <c r="E2" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="21" t="s">
+      <c r="F2" s="19" t="s">
         <v>103</v>
       </c>
-      <c r="F2" s="20" t="s">
+      <c r="G2" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="21" t="s">
+      <c r="H2" s="19" t="s">
         <v>101</v>
       </c>
-      <c r="H2" s="20" t="s">
+      <c r="I2" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="I2" s="22" t="s">
+      <c r="J2" s="20" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="135">
+    <row r="3" spans="1:10" ht="153" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>70</v>
       </c>
-      <c r="B3" s="31" t="s">
+      <c r="B3" s="29" t="s">
         <v>102</v>
       </c>
-      <c r="C3" s="12">
+      <c r="C3" s="10">
         <v>2</v>
       </c>
-      <c r="D3" s="20" t="s">
+      <c r="D3" s="10">
+        <v>2</v>
+      </c>
+      <c r="E3" s="18" t="s">
         <v>183</v>
       </c>
-      <c r="E3" s="21" t="s">
+      <c r="F3" s="19" t="s">
         <v>105</v>
       </c>
-      <c r="F3" s="20" t="s">
+      <c r="G3" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="G3" s="21" t="s">
+      <c r="H3" s="19" t="s">
         <v>106</v>
       </c>
-      <c r="H3" s="20" t="s">
+      <c r="I3" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="I3" s="22" t="s">
+      <c r="J3" s="20" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="195">
+    <row r="4" spans="1:10" ht="221" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>70</v>
       </c>
-      <c r="B4" s="31" t="s">
+      <c r="B4" s="29" t="s">
         <v>102</v>
       </c>
-      <c r="C4" s="12">
+      <c r="C4" s="10">
         <v>3</v>
       </c>
-      <c r="D4" s="20" t="s">
+      <c r="D4" s="10">
+        <v>3</v>
+      </c>
+      <c r="E4" s="18" t="s">
         <v>184</v>
       </c>
-      <c r="E4" s="21" t="s">
+      <c r="F4" s="19" t="s">
         <v>202</v>
       </c>
-      <c r="F4" s="20" t="s">
+      <c r="G4" s="18" t="s">
         <v>190</v>
       </c>
-      <c r="G4" s="21" t="s">
+      <c r="H4" s="19" t="s">
         <v>108</v>
       </c>
-      <c r="H4" s="20" t="s">
+      <c r="I4" s="18" t="s">
         <v>196</v>
       </c>
-      <c r="I4" s="23" t="s">
+      <c r="J4" s="21" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="90">
+    <row r="5" spans="1:10" ht="102" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>70</v>
       </c>
-      <c r="B5" s="31" t="s">
+      <c r="B5" s="29" t="s">
         <v>102</v>
       </c>
-      <c r="C5" s="27">
+      <c r="C5" s="25">
         <v>4</v>
       </c>
-      <c r="D5" s="20" t="s">
+      <c r="D5" s="25">
+        <v>4</v>
+      </c>
+      <c r="E5" s="18" t="s">
         <v>185</v>
       </c>
-      <c r="E5" s="21" t="s">
+      <c r="F5" s="19" t="s">
         <v>109</v>
       </c>
-      <c r="F5" s="20" t="s">
+      <c r="G5" s="18" t="s">
         <v>191</v>
       </c>
-      <c r="G5" s="21" t="s">
+      <c r="H5" s="19" t="s">
         <v>110</v>
       </c>
-      <c r="H5" s="20" t="s">
+      <c r="I5" s="18" t="s">
         <v>197</v>
       </c>
-      <c r="I5" s="22" t="s">
+      <c r="J5" s="20" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="135">
-      <c r="A6" s="28" t="s">
+    <row r="6" spans="1:10" ht="153" x14ac:dyDescent="0.2">
+      <c r="A6" s="26" t="s">
         <v>70</v>
       </c>
-      <c r="B6" s="31" t="s">
+      <c r="B6" s="29" t="s">
         <v>102</v>
       </c>
-      <c r="C6" s="7">
+      <c r="C6" s="5">
         <v>5</v>
       </c>
-      <c r="D6" s="20" t="s">
+      <c r="D6" s="5">
+        <v>5</v>
+      </c>
+      <c r="E6" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="E6" s="21" t="s">
+      <c r="F6" s="19" t="s">
         <v>112</v>
       </c>
-      <c r="F6" s="20" t="s">
+      <c r="G6" s="18" t="s">
         <v>192</v>
       </c>
-      <c r="G6" s="21" t="s">
+      <c r="H6" s="19" t="s">
         <v>113</v>
       </c>
-      <c r="H6" s="20" t="s">
+      <c r="I6" s="18" t="s">
         <v>198</v>
       </c>
-      <c r="I6" s="22" t="s">
+      <c r="J6" s="20" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="75">
-      <c r="A7" s="28" t="s">
+    <row r="7" spans="1:10" ht="102" x14ac:dyDescent="0.2">
+      <c r="A7" s="26" t="s">
         <v>70</v>
       </c>
-      <c r="B7" s="31" t="s">
+      <c r="B7" s="29" t="s">
         <v>93</v>
       </c>
-      <c r="C7" s="7">
+      <c r="C7" s="5">
         <v>6</v>
       </c>
-      <c r="D7" s="20" t="s">
+      <c r="D7" s="5">
+        <v>6</v>
+      </c>
+      <c r="E7" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="E7" s="21" t="s">
+      <c r="F7" s="19" t="s">
         <v>173</v>
       </c>
-      <c r="F7" s="20" t="s">
+      <c r="G7" s="18" t="s">
         <v>193</v>
       </c>
-      <c r="G7" s="21" t="s">
+      <c r="H7" s="19" t="s">
         <v>176</v>
       </c>
-      <c r="H7" s="20" t="s">
+      <c r="I7" s="18" t="s">
         <v>199</v>
       </c>
-      <c r="I7" s="22" t="s">
+      <c r="J7" s="20" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="90">
-      <c r="A8" s="28" t="s">
+    <row r="8" spans="1:10" ht="119" x14ac:dyDescent="0.2">
+      <c r="A8" s="26" t="s">
         <v>71</v>
       </c>
-      <c r="B8" s="31" t="s">
+      <c r="B8" s="29" t="s">
         <v>94</v>
       </c>
-      <c r="C8" s="7">
+      <c r="C8" s="5">
         <v>7</v>
       </c>
-      <c r="D8" s="20" t="s">
+      <c r="D8" s="5">
+        <v>7</v>
+      </c>
+      <c r="E8" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="E8" s="21" t="s">
+      <c r="F8" s="19" t="s">
         <v>126</v>
       </c>
-      <c r="F8" s="20" t="s">
+      <c r="G8" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="G8" s="21" t="s">
+      <c r="H8" s="19" t="s">
         <v>127</v>
       </c>
-      <c r="H8" s="20" t="s">
+      <c r="I8" s="18" t="s">
         <v>100</v>
       </c>
-      <c r="I8" s="22" t="s">
+      <c r="J8" s="20" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="90">
-      <c r="A9" s="28" t="s">
+    <row r="9" spans="1:10" ht="102" x14ac:dyDescent="0.2">
+      <c r="A9" s="26" t="s">
         <v>71</v>
       </c>
-      <c r="B9" s="31" t="s">
+      <c r="B9" s="29" t="s">
         <v>94</v>
       </c>
-      <c r="C9" s="7">
+      <c r="C9" s="5">
         <v>8</v>
       </c>
-      <c r="D9" s="20" t="s">
+      <c r="D9" s="5">
+        <v>8</v>
+      </c>
+      <c r="E9" s="18" t="s">
         <v>186</v>
       </c>
-      <c r="E9" s="21" t="s">
+      <c r="F9" s="19" t="s">
         <v>129</v>
       </c>
-      <c r="F9" s="20" t="s">
+      <c r="G9" s="18" t="s">
         <v>194</v>
       </c>
-      <c r="G9" s="21" t="s">
+      <c r="H9" s="19" t="s">
         <v>130</v>
       </c>
-      <c r="H9" s="20" t="s">
+      <c r="I9" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="I9" s="22" t="s">
+      <c r="J9" s="20" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="75">
-      <c r="A10" s="28" t="s">
+    <row r="10" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+      <c r="A10" s="26" t="s">
         <v>71</v>
       </c>
-      <c r="B10" s="31" t="s">
+      <c r="B10" s="29" t="s">
         <v>94</v>
       </c>
-      <c r="C10" s="7">
+      <c r="C10" s="5">
         <v>9</v>
       </c>
-      <c r="D10" s="20" t="s">
+      <c r="D10" s="5">
+        <v>9</v>
+      </c>
+      <c r="E10" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="E10" s="21" t="s">
+      <c r="F10" s="19" t="s">
         <v>132</v>
       </c>
-      <c r="F10" s="20" t="s">
+      <c r="G10" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="G10" s="21" t="s">
+      <c r="H10" s="19" t="s">
         <v>133</v>
       </c>
-      <c r="H10" s="20" t="s">
+      <c r="I10" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="I10" s="22" t="s">
+      <c r="J10" s="20" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="60">
-      <c r="A11" s="28" t="s">
+    <row r="11" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+      <c r="A11" s="26" t="s">
         <v>72</v>
       </c>
-      <c r="B11" s="31" t="s">
+      <c r="B11" s="29" t="s">
         <v>95</v>
       </c>
-      <c r="C11" s="7">
+      <c r="C11" s="5">
         <v>10</v>
       </c>
-      <c r="D11" s="20" t="s">
+      <c r="D11" s="5">
+        <v>10</v>
+      </c>
+      <c r="E11" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="E11" s="21" t="s">
+      <c r="F11" s="19" t="s">
         <v>135</v>
       </c>
-      <c r="F11" s="20" t="s">
+      <c r="G11" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="G11" s="21" t="s">
+      <c r="H11" s="19" t="s">
         <v>98</v>
       </c>
-      <c r="H11" s="20" t="s">
+      <c r="I11" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="I11" s="22" t="s">
+      <c r="J11" s="20" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="90">
-      <c r="A12" s="28" t="s">
+    <row r="12" spans="1:10" ht="102" x14ac:dyDescent="0.2">
+      <c r="A12" s="26" t="s">
         <v>72</v>
       </c>
-      <c r="B12" s="31" t="s">
+      <c r="B12" s="29" t="s">
         <v>95</v>
       </c>
-      <c r="C12" s="7">
+      <c r="C12" s="5">
         <v>11</v>
       </c>
-      <c r="D12" s="20" t="s">
+      <c r="D12" s="5">
+        <v>11</v>
+      </c>
+      <c r="E12" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="E12" s="21" t="s">
+      <c r="F12" s="19" t="s">
         <v>116</v>
       </c>
-      <c r="F12" s="20" t="s">
+      <c r="G12" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="G12" s="21" t="s">
+      <c r="H12" s="19" t="s">
         <v>136</v>
       </c>
-      <c r="H12" s="20" t="s">
+      <c r="I12" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="I12" s="22" t="s">
+      <c r="J12" s="20" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="60">
-      <c r="A13" s="28" t="s">
+    <row r="13" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+      <c r="A13" s="26" t="s">
         <v>72</v>
       </c>
-      <c r="B13" s="31" t="s">
+      <c r="B13" s="29" t="s">
         <v>95</v>
       </c>
-      <c r="C13" s="7">
+      <c r="C13" s="5">
         <v>12</v>
       </c>
-      <c r="D13" s="20" t="s">
+      <c r="D13" s="5">
+        <v>12</v>
+      </c>
+      <c r="E13" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="E13" s="21" t="s">
+      <c r="F13" s="19" t="s">
         <v>138</v>
       </c>
-      <c r="F13" s="20" t="s">
+      <c r="G13" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="G13" s="21" t="s">
+      <c r="H13" s="19" t="s">
         <v>177</v>
       </c>
-      <c r="H13" s="20" t="s">
+      <c r="I13" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="I13" s="22" t="s">
+      <c r="J13" s="20" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="60">
-      <c r="A14" s="28" t="s">
+    <row r="14" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+      <c r="A14" s="26" t="s">
         <v>72</v>
       </c>
-      <c r="B14" s="31" t="s">
+      <c r="B14" s="29" t="s">
         <v>95</v>
       </c>
-      <c r="C14" s="7">
+      <c r="C14" s="5">
         <v>13</v>
       </c>
-      <c r="D14" s="20" t="s">
+      <c r="D14" s="5">
+        <v>13</v>
+      </c>
+      <c r="E14" s="18" t="s">
         <v>187</v>
       </c>
-      <c r="E14" s="21" t="s">
+      <c r="F14" s="19" t="s">
         <v>174</v>
       </c>
-      <c r="F14" s="20" t="s">
+      <c r="G14" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="G14" s="21" t="s">
+      <c r="H14" s="19" t="s">
         <v>178</v>
       </c>
-      <c r="H14" s="20" t="s">
+      <c r="I14" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="I14" s="22" t="s">
+      <c r="J14" s="20" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="90">
-      <c r="A15" s="28" t="s">
+    <row r="15" spans="1:10" ht="102" x14ac:dyDescent="0.2">
+      <c r="A15" s="26" t="s">
         <v>72</v>
       </c>
-      <c r="B15" s="31" t="s">
+      <c r="B15" s="29" t="s">
         <v>95</v>
       </c>
-      <c r="C15" s="7">
+      <c r="C15" s="5">
         <v>14</v>
       </c>
-      <c r="D15" s="20" t="s">
+      <c r="D15" s="5">
+        <v>14</v>
+      </c>
+      <c r="E15" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="E15" s="21" t="s">
+      <c r="F15" s="19" t="s">
         <v>175</v>
       </c>
-      <c r="F15" s="20" t="s">
+      <c r="G15" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="G15" s="21" t="s">
+      <c r="H15" s="19" t="s">
         <v>203</v>
       </c>
-      <c r="H15" s="20" t="s">
+      <c r="I15" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="I15" s="22" t="s">
+      <c r="J15" s="20" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="60">
-      <c r="A16" s="28" t="s">
+    <row r="16" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+      <c r="A16" s="26" t="s">
         <v>72</v>
       </c>
-      <c r="B16" s="31" t="s">
+      <c r="B16" s="29" t="s">
         <v>95</v>
       </c>
-      <c r="C16" s="7">
+      <c r="C16" s="5">
         <v>15</v>
       </c>
-      <c r="D16" s="20" t="s">
+      <c r="D16" s="5">
+        <v>15</v>
+      </c>
+      <c r="E16" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="E16" s="21" t="s">
+      <c r="F16" s="19" t="s">
         <v>119</v>
       </c>
-      <c r="F16" s="20" t="s">
+      <c r="G16" s="18" t="s">
         <v>195</v>
       </c>
-      <c r="G16" s="21" t="s">
+      <c r="H16" s="19" t="s">
         <v>120</v>
       </c>
-      <c r="H16" s="20" t="s">
+      <c r="I16" s="18" t="s">
         <v>200</v>
       </c>
-      <c r="I16" s="22" t="s">
+      <c r="J16" s="20" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="60">
-      <c r="A17" s="28" t="s">
+    <row r="17" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+      <c r="A17" s="26" t="s">
         <v>72</v>
       </c>
-      <c r="B17" s="31" t="s">
+      <c r="B17" s="29" t="s">
         <v>95</v>
       </c>
-      <c r="C17" s="7">
+      <c r="C17" s="5">
         <v>16</v>
       </c>
-      <c r="D17" s="20" t="s">
+      <c r="D17" s="5">
+        <v>16</v>
+      </c>
+      <c r="E17" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="E17" s="21" t="s">
+      <c r="F17" s="19" t="s">
         <v>140</v>
       </c>
-      <c r="F17" s="20" t="s">
+      <c r="G17" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="G17" s="21" t="s">
+      <c r="H17" s="19" t="s">
         <v>179</v>
       </c>
-      <c r="H17" s="20" t="s">
+      <c r="I17" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="I17" s="22" t="s">
+      <c r="J17" s="20" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="60">
-      <c r="A18" s="28" t="s">
+    <row r="18" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+      <c r="A18" s="26" t="s">
         <v>72</v>
       </c>
-      <c r="B18" s="31" t="s">
+      <c r="B18" s="29" t="s">
         <v>95</v>
       </c>
-      <c r="C18" s="7">
+      <c r="C18" s="5">
         <v>17</v>
       </c>
-      <c r="D18" s="20" t="s">
+      <c r="D18" s="5">
+        <v>17</v>
+      </c>
+      <c r="E18" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="E18" s="21" t="s">
+      <c r="F18" s="19" t="s">
         <v>122</v>
       </c>
-      <c r="F18" s="20" t="s">
+      <c r="G18" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="G18" s="21" t="s">
+      <c r="H18" s="19" t="s">
         <v>123</v>
       </c>
-      <c r="H18" s="20" t="s">
+      <c r="I18" s="18" t="s">
         <v>201</v>
       </c>
-      <c r="I18" s="22" t="s">
+      <c r="J18" s="20" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="75">
-      <c r="A19" s="28" t="s">
+    <row r="19" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+      <c r="A19" s="26" t="s">
         <v>72</v>
       </c>
-      <c r="B19" s="31" t="s">
+      <c r="B19" s="29" t="s">
         <v>95</v>
       </c>
-      <c r="C19" s="7">
+      <c r="C19" s="5">
         <v>18</v>
       </c>
-      <c r="D19" s="20" t="s">
+      <c r="D19" s="5">
+        <v>18</v>
+      </c>
+      <c r="E19" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="E19" s="21" t="s">
+      <c r="F19" s="19" t="s">
         <v>141</v>
       </c>
-      <c r="F19" s="20" t="s">
+      <c r="G19" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="G19" s="21" t="s">
+      <c r="H19" s="19" t="s">
         <v>142</v>
       </c>
-      <c r="H19" s="20" t="s">
+      <c r="I19" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="I19" s="22" t="s">
+      <c r="J19" s="20" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="60">
-      <c r="A20" s="28" t="s">
+    <row r="20" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+      <c r="A20" s="26" t="s">
         <v>72</v>
       </c>
-      <c r="B20" s="31" t="s">
+      <c r="B20" s="29" t="s">
         <v>95</v>
       </c>
-      <c r="C20" s="7">
+      <c r="C20" s="5">
         <v>19</v>
       </c>
-      <c r="D20" s="20" t="s">
+      <c r="D20" s="5">
+        <v>19</v>
+      </c>
+      <c r="E20" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="E20" s="21" t="s">
+      <c r="F20" s="19" t="s">
         <v>144</v>
       </c>
-      <c r="F20" s="20" t="s">
+      <c r="G20" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="G20" s="21" t="s">
+      <c r="H20" s="19" t="s">
         <v>145</v>
       </c>
-      <c r="H20" s="20" t="s">
+      <c r="I20" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="I20" s="22" t="s">
+      <c r="J20" s="20" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="75">
-      <c r="A21" s="28" t="s">
+    <row r="21" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+      <c r="A21" s="26" t="s">
         <v>72</v>
       </c>
-      <c r="B21" s="31" t="s">
+      <c r="B21" s="29" t="s">
         <v>95</v>
       </c>
-      <c r="C21" s="7">
+      <c r="C21" s="5">
         <v>20</v>
       </c>
-      <c r="D21" s="20" t="s">
+      <c r="D21" s="5">
+        <v>20</v>
+      </c>
+      <c r="E21" s="18" t="s">
         <v>188</v>
       </c>
-      <c r="E21" s="21" t="s">
+      <c r="F21" s="19" t="s">
         <v>147</v>
       </c>
-      <c r="F21" s="20" t="s">
+      <c r="G21" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="G21" s="21" t="s">
+      <c r="H21" s="19" t="s">
         <v>148</v>
       </c>
-      <c r="H21" s="20" t="s">
+      <c r="I21" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="I21" s="22" t="s">
+      <c r="J21" s="20" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="60">
-      <c r="A22" s="28" t="s">
+    <row r="22" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+      <c r="A22" s="26" t="s">
         <v>73</v>
       </c>
-      <c r="B22" s="31" t="s">
+      <c r="B22" s="29" t="s">
         <v>96</v>
       </c>
-      <c r="C22" s="7">
+      <c r="C22" s="5">
         <v>21</v>
       </c>
-      <c r="D22" s="20" t="s">
+      <c r="D22" s="5">
+        <v>21</v>
+      </c>
+      <c r="E22" s="18" t="s">
         <v>189</v>
       </c>
-      <c r="E22" s="21" t="s">
+      <c r="F22" s="19" t="s">
         <v>150</v>
       </c>
-      <c r="F22" s="20" t="s">
+      <c r="G22" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="G22" s="21" t="s">
+      <c r="H22" s="19" t="s">
         <v>151</v>
       </c>
-      <c r="H22" s="20" t="s">
+      <c r="I22" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="I22" s="22" t="s">
+      <c r="J22" s="20" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="60">
-      <c r="A23" s="28" t="s">
+    <row r="23" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+      <c r="A23" s="26" t="s">
         <v>73</v>
       </c>
-      <c r="B23" s="31" t="s">
+      <c r="B23" s="29" t="s">
         <v>96</v>
       </c>
-      <c r="C23" s="7">
+      <c r="C23" s="5">
         <v>22</v>
       </c>
-      <c r="D23" s="20" t="s">
+      <c r="D23" s="5">
+        <v>22</v>
+      </c>
+      <c r="E23" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="E23" s="21" t="s">
+      <c r="F23" s="19" t="s">
         <v>153</v>
       </c>
-      <c r="F23" s="20" t="s">
+      <c r="G23" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="G23" s="21" t="s">
+      <c r="H23" s="19" t="s">
         <v>154</v>
       </c>
-      <c r="H23" s="20" t="s">
+      <c r="I23" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="I23" s="22" t="s">
+      <c r="J23" s="20" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="46.8">
-      <c r="A24" s="28" t="s">
+    <row r="24" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="A24" s="26" t="s">
         <v>73</v>
       </c>
-      <c r="B24" s="31" t="s">
+      <c r="B24" s="29" t="s">
         <v>96</v>
       </c>
-      <c r="C24" s="7">
+      <c r="C24" s="5">
         <v>23</v>
       </c>
-      <c r="D24" s="20" t="s">
+      <c r="D24" s="5">
+        <v>23</v>
+      </c>
+      <c r="E24" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="E24" s="21" t="s">
+      <c r="F24" s="19" t="s">
         <v>156</v>
       </c>
-      <c r="F24" s="20" t="s">
+      <c r="G24" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="G24" s="21" t="s">
+      <c r="H24" s="19" t="s">
         <v>157</v>
       </c>
-      <c r="H24" s="20" t="s">
+      <c r="I24" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="I24" s="22" t="s">
+      <c r="J24" s="20" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="46.8">
-      <c r="A25" s="28" t="s">
+    <row r="25" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+      <c r="A25" s="26" t="s">
         <v>74</v>
       </c>
-      <c r="B25" s="31" t="s">
+      <c r="B25" s="29" t="s">
         <v>97</v>
       </c>
-      <c r="C25" s="7">
+      <c r="C25" s="5">
         <v>24</v>
       </c>
-      <c r="D25" s="20" t="s">
+      <c r="D25" s="5">
+        <v>24</v>
+      </c>
+      <c r="E25" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="E25" s="21" t="s">
+      <c r="F25" s="19" t="s">
         <v>159</v>
       </c>
-      <c r="F25" s="20" t="s">
+      <c r="G25" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="G25" s="21" t="s">
+      <c r="H25" s="19" t="s">
         <v>160</v>
       </c>
-      <c r="H25" s="20" t="s">
+      <c r="I25" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="I25" s="22" t="s">
+      <c r="J25" s="20" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="105">
-      <c r="A26" s="28" t="s">
+    <row r="26" spans="1:10" ht="119" x14ac:dyDescent="0.2">
+      <c r="A26" s="26" t="s">
         <v>74</v>
       </c>
-      <c r="B26" s="31" t="s">
+      <c r="B26" s="29" t="s">
         <v>97</v>
       </c>
-      <c r="C26" s="7">
+      <c r="C26" s="5">
         <v>25</v>
       </c>
-      <c r="D26" s="20" t="s">
+      <c r="D26" s="5">
+        <v>25</v>
+      </c>
+      <c r="E26" s="18" t="s">
         <v>54</v>
       </c>
-      <c r="E26" s="21" t="s">
+      <c r="F26" s="19" t="s">
         <v>162</v>
       </c>
-      <c r="F26" s="20" t="s">
+      <c r="G26" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="G26" s="21" t="s">
+      <c r="H26" s="19" t="s">
         <v>163</v>
       </c>
-      <c r="H26" s="20" t="s">
+      <c r="I26" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="I26" s="22" t="s">
+      <c r="J26" s="20" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="120.6" thickBot="1">
-      <c r="A27" s="28" t="s">
+    <row r="27" spans="1:10" ht="137" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="26" t="s">
         <v>74</v>
       </c>
-      <c r="B27" s="31" t="s">
+      <c r="B27" s="29" t="s">
         <v>97</v>
       </c>
-      <c r="C27" s="8">
+      <c r="C27" s="6">
         <v>26</v>
       </c>
-      <c r="D27" s="24" t="s">
+      <c r="D27" s="6">
+        <v>26</v>
+      </c>
+      <c r="E27" s="22" t="s">
         <v>57</v>
       </c>
-      <c r="E27" s="25" t="s">
+      <c r="F27" s="23" t="s">
         <v>165</v>
       </c>
-      <c r="F27" s="24" t="s">
+      <c r="G27" s="22" t="s">
         <v>58</v>
       </c>
-      <c r="G27" s="25" t="s">
+      <c r="H27" s="23" t="s">
         <v>204</v>
       </c>
-      <c r="H27" s="24" t="s">
+      <c r="I27" s="22" t="s">
         <v>59</v>
       </c>
-      <c r="I27" s="26" t="s">
+      <c r="J27" s="24" t="s">
         <v>166</v>
       </c>
     </row>
@@ -2359,59 +2482,106 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A98B4A3-5095-AF4B-B22C-B7631D8C258B}">
-  <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.6"/>
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
     <col min="2" max="2" width="32.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="19.8">
-      <c r="A1" s="15" t="s">
+    <row r="1" spans="1:2" ht="21" x14ac:dyDescent="0.25">
+      <c r="A1" s="13" t="s">
         <v>75</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="11" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="114.9" customHeight="1">
-      <c r="A2" s="15" t="s">
+    <row r="2" spans="1:2" ht="21" x14ac:dyDescent="0.25">
+      <c r="A2" s="32" t="s">
+        <v>208</v>
+      </c>
+      <c r="B2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="115" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="B2" s="14" t="s">
+      <c r="B3" s="12" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="62.4">
-      <c r="A3" s="15" t="s">
+    <row r="4" spans="1:2" ht="68" x14ac:dyDescent="0.25">
+      <c r="A4" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="B3" s="29" t="s">
+      <c r="B4" s="27" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="79.2">
-      <c r="A4" s="15" t="s">
+    <row r="5" spans="1:2" ht="85" x14ac:dyDescent="0.25">
+      <c r="A5" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="B4" s="14" t="s">
+      <c r="B5" s="12" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="79.2">
-      <c r="A5" s="15" t="s">
+    <row r="6" spans="1:2" ht="85" x14ac:dyDescent="0.25">
+      <c r="A6" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="B5" s="14" t="s">
+      <c r="B6" s="12" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="79.2">
-      <c r="A6" s="15" t="s">
+    <row r="7" spans="1:2" ht="85" x14ac:dyDescent="0.25">
+      <c r="A7" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="B6" s="14" t="s">
+      <c r="B7" s="12" t="s">
         <v>124</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2FD1CDDF-9E3E-E24C-A67F-EA5A7DE12C6E}">
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="24.5" style="30" customWidth="1"/>
+    <col min="2" max="2" width="27.1640625" style="30" customWidth="1"/>
+    <col min="3" max="16384" width="11" style="30"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1" s="30" t="s">
+        <v>75</v>
+      </c>
+      <c r="B1" s="30" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" s="30" t="s">
+        <v>206</v>
+      </c>
+      <c r="B2" s="30" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" s="30" t="s">
+        <v>205</v>
+      </c>
+      <c r="B3" s="31" t="s">
+        <v>210</v>
       </c>
     </row>
   </sheetData>
